--- a/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
@@ -23,13 +23,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>2222249_PWE01_1779771515934</t>
-  </si>
-  <si>
-    <t>2222249_PWE02_1779771515934</t>
-  </si>
-  <si>
-    <t>2222249_PWE03_1779771515934</t>
+    <t>2222249_PWE01_1780205715773</t>
+  </si>
+  <si>
+    <t>2222249_PWE02_1780205715773</t>
+  </si>
+  <si>
+    <t>2222249_PWE03_1780205715773</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
@@ -23,13 +23,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>2222249_PWE01_1780205715773</t>
-  </si>
-  <si>
-    <t>2222249_PWE02_1780205715773</t>
-  </si>
-  <si>
-    <t>2222249_PWE03_1780205715773</t>
+    <t>2222249_PWE01_1780426302169</t>
+  </si>
+  <si>
+    <t>2222249_PWE02_1780426302169</t>
+  </si>
+  <si>
+    <t>2222249_PWE03_1780426302169</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports05/UK_InHeader_ImportTb.xlsx
@@ -23,13 +23,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>2222249_PWE01_1780426302169</t>
-  </si>
-  <si>
-    <t>2222249_PWE02_1780426302169</t>
-  </si>
-  <si>
-    <t>2222249_PWE03_1780426302169</t>
+    <t>2222249_PWE01_1780464842872</t>
+  </si>
+  <si>
+    <t>2222249_PWE02_1780464842872</t>
+  </si>
+  <si>
+    <t>2222249_PWE03_1780464842872</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>
